--- a/artfynd/A 30828-2025 artfynd.xlsx
+++ b/artfynd/A 30828-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96052128</v>
+        <v>96052140</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ursåsen, Jmt</t>
+          <t>ursåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533994.5492193899</v>
+        <v>533995</v>
       </c>
       <c r="R2" t="n">
-        <v>7100744.617576702</v>
+        <v>7100733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96052157</v>
+        <v>96052128</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,14 +814,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ursåsen, Jmt</t>
+          <t>Ursåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534030.6464113102</v>
+        <v>533995</v>
       </c>
       <c r="R3" t="n">
-        <v>7100734.929809069</v>
+        <v>7100744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,126 +878,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>96052140</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>ursåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>533994.6832176687</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7100732.345164339</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 30828-2025 artfynd.xlsx
+++ b/artfynd/A 30828-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96052140</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,8 +892,17 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96052128</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>